--- a/doctool/test/auto/scenario08/システム機能設計書_サンプル_S08_レビュー記録票_expected.xlsx
+++ b/doctool/test/auto/scenario08/システム機能設計書_サンプル_S08_レビュー記録票_expected.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" updateLinks="never" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED57F6F-38D7-4EB5-9829-ABD4A9065B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20630C3-7F0A-41B1-A9A6-36B0B20D464B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="レビュー実施状況" sheetId="3" r:id="rId1"/>
@@ -4888,7 +4888,7 @@
       <c r="C6" s="157"/>
       <c r="D6" s="158">
         <f>SUM(レビュー時間)</f>
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E6" s="159"/>
       <c r="F6" s="76" t="s">
@@ -5160,18 +5160,12 @@
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
-      <c r="D15" s="16">
-        <v>45139.375</v>
-      </c>
-      <c r="E15" s="16">
-        <v>45139.583333333336</v>
-      </c>
-      <c r="F15" s="17">
-        <v>200</v>
-      </c>
-      <c r="G15" s="18">
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="18" t="str">
         <f t="shared" ref="G15" si="0">IF(F15&lt;&gt;"",F15/60*N15,"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="H15" s="19" t="s">
         <v>193</v>
